--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1239"/>
+  <dimension ref="A1:B1240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15296,6 +15296,18 @@
         </is>
       </c>
     </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>BK服飾</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1240"/>
+  <dimension ref="A1:B1241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15308,6 +15308,18 @@
         </is>
       </c>
     </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>YIYI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/AG/廠商代碼.xlsx
+++ b/data/AG/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1241"/>
+  <dimension ref="A1:B1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15320,6 +15320,18 @@
         </is>
       </c>
     </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>肖霞</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
